--- a/scripts/Exaspim_ingest/ExM Sample Tracking.xlsx
+++ b/scripts/Exaspim_ingest/ExM Sample Tracking.xlsx
@@ -114,13 +114,13 @@
     <t>Immuno: Secondary Antibody1</t>
   </si>
   <si>
-    <t>Mass of Secondary Antibody used per Brain (ug)</t>
-  </si>
-  <si>
-    <t>Secondary Antibody Catalog #</t>
-  </si>
-  <si>
-    <t>Secondary Antibody Lot #</t>
+    <t>Mass of Secondary Antibody1 used per Brain (ug)</t>
+  </si>
+  <si>
+    <t>Secondary Antibody1 Catalog #</t>
+  </si>
+  <si>
+    <t>Secondary Antibody1 Lot #</t>
   </si>
   <si>
     <t>Immuno: Secondary Antibody2</t>
